--- a/data/test_tomato_data.xlsx
+++ b/data/test_tomato_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dana/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362DC772-8150-E94C-9036-888789F4F195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C00DAE-A6B6-5F4E-84E4-E43FEDBE37E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="840" windowWidth="28100" windowHeight="17380" xr2:uid="{CA579793-98E6-7F4F-82B2-D5D408A600F2}"/>
   </bookViews>
@@ -555,28 +555,31 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>77</v>
+        <v>86.1</v>
       </c>
       <c r="I2">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>5.5</v>
+        <v>6.1</v>
+      </c>
+      <c r="L2">
+        <v>84.2</v>
       </c>
       <c r="M2">
-        <v>2000</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
